--- a/survey_templates/037_organizational_structure_survey--survey_templates.xlsx
+++ b/survey_templates/037_organizational_structure_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id:ประก':_'team_member'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id:ประก': 'Team Member'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'executive'}</t>
+          <t>executive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Executive'}</t>
+          <t>Executive</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'flat'}</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Flat'}</t>
+          <t>Flat</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hierarchy'}</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hierarchy'}</t>
+          <t>Hierarchy</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'department'}</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Department'}</t>
+          <t>Department</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'company'}</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Company'}</t>
+          <t>Company</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'complex'}</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Complex'}</t>
+          <t>Complex</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'flat'}</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Flat'}</t>
+          <t>Flat</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hierarchy'}</t>
+          <t>hierarchy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hierarchy'}</t>
+          <t>Hierarchy</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'line'}</t>
+          <t>line</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Line'}</t>
+          <t>Line</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'matrix'}</t>
+          <t>matrix</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Matrix'}</t>
+          <t>Matrix</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'complex'}</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Complex'}</t>
+          <t>Complex</t>
         </is>
       </c>
     </row>
